--- a/reports/Angola_2.2_exports_HS-AG6-2003-2024_reverse_top_25.xlsx
+++ b/reports/Angola_2.2_exports_HS-AG6-2003-2024_reverse_top_25.xlsx
@@ -400,15 +400,15 @@
     <t>740321</t>
   </si>
   <si>
+    <t>847990</t>
+  </si>
+  <si>
+    <t>732690</t>
+  </si>
+  <si>
     <t>280469</t>
   </si>
   <si>
-    <t>847990</t>
-  </si>
-  <si>
-    <t>732690</t>
-  </si>
-  <si>
     <t>854460</t>
   </si>
   <si>
@@ -814,13 +814,13 @@
     <t>Copper; copper-zinc base alloys (brass) unwrought</t>
   </si>
   <si>
+    <t>Machines and mechanical appliances; parts, of those having individual functions</t>
+  </si>
+  <si>
+    <t>Iron or steel; articles n.e.c. in heading 7326</t>
+  </si>
+  <si>
     <t>Silicon; containing by weight less than 99.99% of silicon</t>
-  </si>
-  <si>
-    <t>Machines and mechanical appliances; parts, of those having individual functions</t>
-  </si>
-  <si>
-    <t>Iron or steel; articles n.e.c. in heading 7326</t>
   </si>
   <si>
     <t>Insulated electric conductors; for a voltage exceeding 1000 volts</t>
@@ -3180,10 +3180,10 @@
         <v>30669817185.095</v>
       </c>
       <c r="G77">
-        <v>0.9590327659668231</v>
+        <v>0.9590373944062209</v>
       </c>
       <c r="H77">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3206,10 +3206,10 @@
         <v>555402540</v>
       </c>
       <c r="G78">
-        <v>0.01736721255776045</v>
+        <v>0.01736729637459516</v>
       </c>
       <c r="H78">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3232,10 +3232,10 @@
         <v>258742278</v>
       </c>
       <c r="G79">
-        <v>0.008090766275042863</v>
+        <v>0.008090805322323326</v>
       </c>
       <c r="H79">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3258,10 +3258,10 @@
         <v>137208332</v>
       </c>
       <c r="G80">
-        <v>0.004290448989555872</v>
+        <v>0.004290469695921537</v>
       </c>
       <c r="H80">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3284,10 +3284,10 @@
         <v>91686471.434</v>
       </c>
       <c r="G81">
-        <v>0.002866998840274136</v>
+        <v>0.002867012676850796</v>
       </c>
       <c r="H81">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -3310,10 +3310,10 @@
         <v>67104055</v>
       </c>
       <c r="G82">
-        <v>0.002098316631163854</v>
+        <v>0.002098326757962134</v>
       </c>
       <c r="H82">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3336,10 +3336,10 @@
         <v>53132388</v>
       </c>
       <c r="G83">
-        <v>0.001661428260838347</v>
+        <v>0.001661436279146263</v>
       </c>
       <c r="H83">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3362,10 +3362,10 @@
         <v>23547581.594</v>
       </c>
       <c r="G84">
-        <v>0.000736323342641187</v>
+        <v>0.0007363268962507086</v>
       </c>
       <c r="H84">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -3388,10 +3388,10 @@
         <v>19267739.973</v>
       </c>
       <c r="G85">
-        <v>0.0006024944279490485</v>
+        <v>0.0006024973356796769</v>
       </c>
       <c r="H85">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3414,10 +3414,10 @@
         <v>18632262.965</v>
       </c>
       <c r="G86">
-        <v>0.0005826233191969971</v>
+        <v>0.0005826261310266032</v>
       </c>
       <c r="H86">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -3440,10 +3440,10 @@
         <v>13237621</v>
       </c>
       <c r="G87">
-        <v>0.0004139350491016361</v>
+        <v>0.000413937046815747</v>
       </c>
       <c r="H87">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3466,10 +3466,10 @@
         <v>11879093</v>
       </c>
       <c r="G88">
-        <v>0.000371454428574281</v>
+        <v>0.0003714562212703939</v>
       </c>
       <c r="H88">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -3492,10 +3492,10 @@
         <v>6242443.323</v>
       </c>
       <c r="G89">
-        <v>0.0001951986753073068</v>
+        <v>0.0001951996173660885</v>
       </c>
       <c r="H89">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3518,10 +3518,10 @@
         <v>3815940.581</v>
       </c>
       <c r="G90">
-        <v>0.0001193229169928011</v>
+        <v>0.0001193234928635218</v>
       </c>
       <c r="H90">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3544,10 +3544,10 @@
         <v>3382641</v>
       </c>
       <c r="G91">
-        <v>0.0001057738145266591</v>
+        <v>0.0001057743250073307</v>
       </c>
       <c r="H91">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -3570,10 +3570,10 @@
         <v>3150644</v>
       </c>
       <c r="G92">
-        <v>9.851936226620896E-05</v>
+        <v>9.85198377357799E-05</v>
       </c>
       <c r="H92">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3596,10 +3596,10 @@
         <v>2608824.962</v>
       </c>
       <c r="G93">
-        <v>8.157690031638193E-05</v>
+        <v>8.157729401902982E-05</v>
       </c>
       <c r="H93">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3622,10 +3622,10 @@
         <v>2463038.497</v>
       </c>
       <c r="G94">
-        <v>7.701821658097895E-05</v>
+        <v>7.70185882827191E-05</v>
       </c>
       <c r="H94">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3648,10 +3648,10 @@
         <v>2222302.982</v>
       </c>
       <c r="G95">
-        <v>6.949051449447618E-05</v>
+        <v>6.949084986637011E-05</v>
       </c>
       <c r="H95">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3674,10 +3674,10 @@
         <v>1893175</v>
       </c>
       <c r="G96">
-        <v>5.919881575269378E-05</v>
+        <v>5.919910145526918E-05</v>
       </c>
       <c r="H96">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3700,10 +3700,10 @@
         <v>1711523.561</v>
       </c>
       <c r="G97">
-        <v>5.351864880110573E-05</v>
+        <v>5.351890709032318E-05</v>
       </c>
       <c r="H97">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3726,10 +3726,10 @@
         <v>1416899.661</v>
       </c>
       <c r="G98">
-        <v>4.430587873365816E-05</v>
+        <v>4.430609256063254E-05</v>
       </c>
       <c r="H98">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3752,10 +3752,10 @@
         <v>1412334.218</v>
       </c>
       <c r="G99">
-        <v>4.416311917947726E-05</v>
+        <v>4.416333231747211E-05</v>
       </c>
       <c r="H99">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3778,10 +3778,10 @@
         <v>1247088.85</v>
       </c>
       <c r="G100">
-        <v>3.899596342566787E-05</v>
+        <v>3.899615162617559E-05</v>
       </c>
       <c r="H100">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3804,10 +3804,10 @@
         <v>1218835.434</v>
       </c>
       <c r="G101">
-        <v>3.811249054642099E-05</v>
+        <v>3.811267448315293E-05</v>
       </c>
       <c r="H101">
-        <v>31979947164.971</v>
+        <v>31979792825.58</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3830,10 +3830,10 @@
         <v>38353255495.958</v>
       </c>
       <c r="G102">
-        <v>0.9196365785127872</v>
+        <v>0.919629632404436</v>
       </c>
       <c r="H102">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3856,10 +3856,10 @@
         <v>756137431.048</v>
       </c>
       <c r="G103">
-        <v>0.01813070705426077</v>
+        <v>0.01813057011119149</v>
       </c>
       <c r="H103">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3882,10 +3882,10 @@
         <v>685462362</v>
       </c>
       <c r="G104">
-        <v>0.01643605616100589</v>
+        <v>0.01643593201780669</v>
       </c>
       <c r="H104">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3908,10 +3908,10 @@
         <v>629137625</v>
       </c>
       <c r="G105">
-        <v>0.01508549835957567</v>
+        <v>0.01508538441727652</v>
       </c>
       <c r="H105">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -3934,10 +3934,10 @@
         <v>305203367.76</v>
       </c>
       <c r="G106">
-        <v>0.007318184004144483</v>
+        <v>0.007318128729158456</v>
       </c>
       <c r="H106">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3960,10 +3960,10 @@
         <v>178500294.133</v>
       </c>
       <c r="G107">
-        <v>0.004280090376612186</v>
+        <v>0.004280058048655466</v>
       </c>
       <c r="H107">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -3986,10 +3986,10 @@
         <v>159385183</v>
       </c>
       <c r="G108">
-        <v>0.003821747136307685</v>
+        <v>0.003821718270263945</v>
       </c>
       <c r="H108">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -4012,10 +4012,10 @@
         <v>122286961</v>
       </c>
       <c r="G109">
-        <v>0.002932203823548137</v>
+        <v>0.00293218167631526</v>
       </c>
       <c r="H109">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -4038,10 +4038,10 @@
         <v>122186195</v>
       </c>
       <c r="G110">
-        <v>0.002929787650572151</v>
+        <v>0.002929765521588874</v>
       </c>
       <c r="H110">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -4064,10 +4064,10 @@
         <v>103522643.448</v>
       </c>
       <c r="G111">
-        <v>0.002482271932017642</v>
+        <v>0.002482253183165977</v>
       </c>
       <c r="H111">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -4090,10 +4090,10 @@
         <v>62795113.292</v>
       </c>
       <c r="G112">
-        <v>0.001505704858385849</v>
+        <v>0.001505693485644338</v>
       </c>
       <c r="H112">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -4116,10 +4116,10 @@
         <v>20730589.106</v>
       </c>
       <c r="G113">
-        <v>0.0004970792645752195</v>
+        <v>0.0004970755100851182</v>
       </c>
       <c r="H113">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -4142,10 +4142,10 @@
         <v>16422626</v>
       </c>
       <c r="G114">
-        <v>0.0003937826760606231</v>
+        <v>0.0003937797017801315</v>
       </c>
       <c r="H114">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -4168,10 +4168,10 @@
         <v>15936965.32</v>
       </c>
       <c r="G115">
-        <v>0.000382137476186509</v>
+        <v>0.0003821345898633933</v>
       </c>
       <c r="H115">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -4194,10 +4194,10 @@
         <v>15477720</v>
       </c>
       <c r="G116">
-        <v>0.0003711256653422557</v>
+        <v>0.0003711228621924641</v>
       </c>
       <c r="H116">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -4220,10 +4220,10 @@
         <v>12125845</v>
       </c>
       <c r="G117">
-        <v>0.0002907542127304321</v>
+        <v>0.0002907520166343738</v>
       </c>
       <c r="H117">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -4246,10 +4246,10 @@
         <v>9526215.425000001</v>
       </c>
       <c r="G118">
-        <v>0.0002284201444267492</v>
+        <v>0.0002284184191462309</v>
       </c>
       <c r="H118">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -4272,10 +4272,10 @@
         <v>5627488</v>
       </c>
       <c r="G119">
-        <v>0.0001349362327400651</v>
+        <v>0.0001349352135530133</v>
       </c>
       <c r="H119">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -4298,10 +4298,10 @@
         <v>4677170</v>
       </c>
       <c r="G120">
-        <v>0.0001121494527726847</v>
+        <v>0.0001121486056964932</v>
       </c>
       <c r="H120">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -4324,10 +4324,10 @@
         <v>4529673.597</v>
       </c>
       <c r="G121">
-        <v>0.0001086127754908264</v>
+        <v>0.0001086119551275171</v>
       </c>
       <c r="H121">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4350,10 +4350,10 @@
         <v>4499876</v>
       </c>
       <c r="G122">
-        <v>0.0001078982869865619</v>
+        <v>0.0001078974720198567</v>
       </c>
       <c r="H122">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4376,10 +4376,10 @@
         <v>4492104.146</v>
       </c>
       <c r="G123">
-        <v>0.0001077119330218505</v>
+        <v>0.0001077111194626957</v>
       </c>
       <c r="H123">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4402,10 +4402,10 @@
         <v>4454661.299</v>
       </c>
       <c r="G124">
-        <v>0.0001068141262709089</v>
+        <v>0.0001068133194929796</v>
       </c>
       <c r="H124">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4428,10 +4428,10 @@
         <v>3220589</v>
       </c>
       <c r="G125">
-        <v>7.72234693106575E-05</v>
+        <v>7.722288603396144E-05</v>
       </c>
       <c r="H125">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -4454,10 +4454,10 @@
         <v>3069328</v>
       </c>
       <c r="G126">
-        <v>7.359652430420081E-05</v>
+        <v>7.359596842218824E-05</v>
       </c>
       <c r="H126">
-        <v>41704795559.548</v>
+        <v>41705110562.478</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -10330,10 +10330,10 @@
         <v>31630754657.761</v>
       </c>
       <c r="G352">
-        <v>0.8616590822021356</v>
+        <v>0.861622836858379</v>
       </c>
       <c r="H352">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -10356,10 +10356,10 @@
         <v>2478615454.372</v>
       </c>
       <c r="G353">
-        <v>0.06752040982437264</v>
+        <v>0.06751756960540992</v>
       </c>
       <c r="H353">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -10382,10 +10382,10 @@
         <v>1040977736.293</v>
       </c>
       <c r="G354">
-        <v>0.02835746192438697</v>
+        <v>0.02835626907912282</v>
       </c>
       <c r="H354">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -10408,10 +10408,10 @@
         <v>351839752.77</v>
       </c>
       <c r="G355">
-        <v>0.009584530047867162</v>
+        <v>0.009584126878454216</v>
       </c>
       <c r="H355">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -10434,10 +10434,10 @@
         <v>202151176.583</v>
       </c>
       <c r="G356">
-        <v>0.005506836595119018</v>
+        <v>0.005506604952245957</v>
       </c>
       <c r="H356">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -10460,10 +10460,10 @@
         <v>181861682.224</v>
       </c>
       <c r="G357">
-        <v>0.00495412682651311</v>
+        <v>0.004953918433154821</v>
       </c>
       <c r="H357">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -10486,10 +10486,10 @@
         <v>106322324.286</v>
       </c>
       <c r="G358">
-        <v>0.002896345577369715</v>
+        <v>0.002896223743754475</v>
       </c>
       <c r="H358">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -10512,10 +10512,10 @@
         <v>104607138.31</v>
       </c>
       <c r="G359">
-        <v>0.002849621887407942</v>
+        <v>0.002849502019205983</v>
       </c>
       <c r="H359">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -10538,10 +10538,10 @@
         <v>50162179.26</v>
       </c>
       <c r="G360">
-        <v>0.001366476956054078</v>
+        <v>0.001366419475748896</v>
       </c>
       <c r="H360">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -10564,10 +10564,10 @@
         <v>38140674.031</v>
       </c>
       <c r="G361">
-        <v>0.001038996967846881</v>
+        <v>0.001038953262856079</v>
       </c>
       <c r="H361">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -10590,10 +10590,10 @@
         <v>34674977.243</v>
       </c>
       <c r="G362">
-        <v>0.0009445872977062335</v>
+        <v>0.0009445475640203469</v>
       </c>
       <c r="H362">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -10616,10 +10616,10 @@
         <v>28734289.94</v>
       </c>
       <c r="G363">
-        <v>0.0007827559653672535</v>
+        <v>0.0007827230390514653</v>
       </c>
       <c r="H363">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -10642,10 +10642,10 @@
         <v>26040461.061</v>
       </c>
       <c r="G364">
-        <v>0.000709372887897136</v>
+        <v>0.0007093430484110742</v>
       </c>
       <c r="H364">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -10668,10 +10668,10 @@
         <v>25452667.39</v>
       </c>
       <c r="G365">
-        <v>0.0006933606946833453</v>
+        <v>0.0006933315287437698</v>
       </c>
       <c r="H365">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -10694,10 +10694,10 @@
         <v>23279825.335</v>
       </c>
       <c r="G366">
-        <v>0.000634169913080475</v>
+        <v>0.0006341432369773915</v>
       </c>
       <c r="H366">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -10720,10 +10720,10 @@
         <v>20386572.634</v>
       </c>
       <c r="G367">
-        <v>0.0005553542953724473</v>
+        <v>0.0005553309346167165</v>
       </c>
       <c r="H367">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -10746,10 +10746,10 @@
         <v>20027369.156</v>
       </c>
       <c r="G368">
-        <v>0.0005455691687598783</v>
+        <v>0.0005455462196115746</v>
       </c>
       <c r="H368">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -10772,10 +10772,10 @@
         <v>19538534.039</v>
       </c>
       <c r="G369">
-        <v>0.0005322527233313769</v>
+        <v>0.00053223033433401</v>
       </c>
       <c r="H369">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -10798,10 +10798,10 @@
         <v>19392524.306</v>
       </c>
       <c r="G370">
-        <v>0.0005282752459081979</v>
+        <v>0.0005282530242218238</v>
       </c>
       <c r="H370">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -10824,10 +10824,10 @@
         <v>18257387.404</v>
       </c>
       <c r="G371">
-        <v>0.0004973527771990579</v>
+        <v>0.0004973318562539298</v>
       </c>
       <c r="H371">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -10850,10 +10850,10 @@
         <v>12670818.135</v>
       </c>
       <c r="G372">
-        <v>0.0003451680379770966</v>
+        <v>0.0003451535186219959</v>
       </c>
       <c r="H372">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -10876,10 +10876,10 @@
         <v>11964566.786</v>
       </c>
       <c r="G373">
-        <v>0.0003259289178306526</v>
+        <v>0.0003259152077614257</v>
       </c>
       <c r="H373">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -10902,10 +10902,10 @@
         <v>10305903.529</v>
       </c>
       <c r="G374">
-        <v>0.000280744973433096</v>
+        <v>0.0002807331640083708</v>
       </c>
       <c r="H374">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -10928,10 +10928,10 @@
         <v>9998539.368999999</v>
       </c>
       <c r="G375">
-        <v>0.0002723720110149373</v>
+        <v>0.0002723605537955186</v>
       </c>
       <c r="H375">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -10954,10 +10954,10 @@
         <v>9793481.878</v>
       </c>
       <c r="G376">
-        <v>0.0002667860029855532</v>
+        <v>0.0002667747807393222</v>
       </c>
       <c r="H376">
-        <v>36709129296.151</v>
+        <v>36710673515.911</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -10980,10 +10980,10 @@
         <v>38649162649.402</v>
       </c>
       <c r="G377">
-        <v>0.8746116592468505</v>
+        <v>0.8745788708245871</v>
       </c>
       <c r="H377">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -11006,10 +11006,10 @@
         <v>2208487556.289</v>
       </c>
       <c r="G378">
-        <v>0.04997699390162157</v>
+        <v>0.0499751203080533</v>
       </c>
       <c r="H378">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="379" spans="1:8">
@@ -11032,10 +11032,10 @@
         <v>1520604099.421</v>
       </c>
       <c r="G379">
-        <v>0.03441052750654459</v>
+        <v>0.03440923748611752</v>
       </c>
       <c r="H379">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -11058,10 +11058,10 @@
         <v>407918898.824</v>
       </c>
       <c r="G380">
-        <v>0.009231005291756997</v>
+        <v>0.009230659229483277</v>
       </c>
       <c r="H380">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -11084,10 +11084,10 @@
         <v>301511758.088</v>
       </c>
       <c r="G381">
-        <v>0.006823063708156711</v>
+        <v>0.006822807917496219</v>
       </c>
       <c r="H381">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -11110,10 +11110,10 @@
         <v>252740987.415</v>
       </c>
       <c r="G382">
-        <v>0.005719405006725047</v>
+        <v>0.005719190591259082</v>
       </c>
       <c r="H382">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -11136,10 +11136,10 @@
         <v>131604060.394</v>
       </c>
       <c r="G383">
-        <v>0.00297813555933792</v>
+        <v>0.002978023911653779</v>
       </c>
       <c r="H383">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -11162,10 +11162,10 @@
         <v>109133110.157</v>
       </c>
       <c r="G384">
-        <v>0.002469628939157881</v>
+        <v>0.002469536354939921</v>
       </c>
       <c r="H384">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -11188,10 +11188,10 @@
         <v>57525715.868</v>
       </c>
       <c r="G385">
-        <v>0.001301778831822966</v>
+        <v>0.001301730029278911</v>
       </c>
       <c r="H385">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -11214,10 +11214,10 @@
         <v>50817243.996</v>
       </c>
       <c r="G386">
-        <v>0.001149969392425667</v>
+        <v>0.001149926281084045</v>
       </c>
       <c r="H386">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -11240,10 +11240,10 @@
         <v>40507306.07600001</v>
       </c>
       <c r="G387">
-        <v>0.0009166605367399481</v>
+        <v>0.0009166261719422313</v>
       </c>
       <c r="H387">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -11266,10 +11266,10 @@
         <v>26146439.672</v>
       </c>
       <c r="G388">
-        <v>0.0005916811495340229</v>
+        <v>0.000591658967927854</v>
       </c>
       <c r="H388">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -11292,10 +11292,10 @@
         <v>26048990.57</v>
       </c>
       <c r="G389">
-        <v>0.0005894759239883756</v>
+        <v>0.0005894538250541738</v>
       </c>
       <c r="H389">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -11315,13 +11315,13 @@
         <v>138</v>
       </c>
       <c r="F390">
-        <v>23461338.702</v>
+        <v>23461716.9</v>
       </c>
       <c r="G390">
-        <v>0.000530918627046272</v>
+        <v>0.0005309072814886873</v>
       </c>
       <c r="H390">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -11344,10 +11344,10 @@
         <v>20447680.218</v>
       </c>
       <c r="G391">
-        <v>0.0004627210086139005</v>
+        <v>0.0004627036616100501</v>
       </c>
       <c r="H391">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -11370,10 +11370,10 @@
         <v>19075797.033</v>
       </c>
       <c r="G392">
-        <v>0.0004316759627066958</v>
+        <v>0.0004316597795543257</v>
       </c>
       <c r="H392">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -11396,10 +11396,10 @@
         <v>17094204.575</v>
       </c>
       <c r="G393">
-        <v>0.0003868334939742136</v>
+        <v>0.0003868189919265769</v>
       </c>
       <c r="H393">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="394" spans="1:8">
@@ -11422,10 +11422,10 @@
         <v>15872972.252</v>
       </c>
       <c r="G394">
-        <v>0.0003591976034367134</v>
+        <v>0.0003591841374343192</v>
       </c>
       <c r="H394">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="395" spans="1:8">
@@ -11448,10 +11448,10 @@
         <v>14359200.295</v>
       </c>
       <c r="G395">
-        <v>0.0003249416839736405</v>
+        <v>0.0003249295021955536</v>
       </c>
       <c r="H395">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="396" spans="1:8">
@@ -11474,10 +11474,10 @@
         <v>14151101.015</v>
       </c>
       <c r="G396">
-        <v>0.0003202324989850832</v>
+        <v>0.0003202204937502019</v>
       </c>
       <c r="H396">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="397" spans="1:8">
@@ -11500,10 +11500,10 @@
         <v>9881790.873</v>
       </c>
       <c r="G397">
-        <v>0.0002236200972881527</v>
+        <v>0.0002236117139672823</v>
       </c>
       <c r="H397">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="398" spans="1:8">
@@ -11526,10 +11526,10 @@
         <v>9876788.351</v>
       </c>
       <c r="G398">
-        <v>0.0002235068926604994</v>
+        <v>0.0002234985135835709</v>
       </c>
       <c r="H398">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="399" spans="1:8">
@@ -11552,10 +11552,10 @@
         <v>9864064.896</v>
       </c>
       <c r="G399">
-        <v>0.0002232189670930078</v>
+        <v>0.0002232105988101558</v>
       </c>
       <c r="H399">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="400" spans="1:8">
@@ -11578,10 +11578,10 @@
         <v>9569631.807</v>
       </c>
       <c r="G400">
-        <v>0.000216556090206296</v>
+        <v>0.0002165479717088414</v>
       </c>
       <c r="H400">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="401" spans="1:8">
@@ -11604,10 +11604,10 @@
         <v>9392419.198000001</v>
       </c>
       <c r="G401">
-        <v>0.000212545855485225</v>
+        <v>0.0002125378873279448</v>
       </c>
       <c r="H401">
-        <v>44190083954.156</v>
+        <v>44191740663.666</v>
       </c>
     </row>
     <row r="402" spans="1:8">
@@ -11630,10 +11630,10 @@
         <v>32819544545.163</v>
       </c>
       <c r="G402">
-        <v>0.8748799211735858</v>
+        <v>0.8748503564101066</v>
       </c>
       <c r="H402">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="403" spans="1:8">
@@ -11656,10 +11656,10 @@
         <v>1599071870.665</v>
       </c>
       <c r="G403">
-        <v>0.04262691306496146</v>
+        <v>0.04262547257630455</v>
       </c>
       <c r="H403">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="404" spans="1:8">
@@ -11682,10 +11682,10 @@
         <v>1306647522.475</v>
       </c>
       <c r="G404">
-        <v>0.03483167415353636</v>
+        <v>0.03483049708890953</v>
       </c>
       <c r="H404">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="405" spans="1:8">
@@ -11708,10 +11708,10 @@
         <v>440201044.661</v>
       </c>
       <c r="G405">
-        <v>0.01173456428450973</v>
+        <v>0.01173416773909909</v>
       </c>
       <c r="H405">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="406" spans="1:8">
@@ -11734,10 +11734,10 @@
         <v>229382276.953</v>
       </c>
       <c r="G406">
-        <v>0.006114708511664435</v>
+        <v>0.006114501877694999</v>
       </c>
       <c r="H406">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="407" spans="1:8">
@@ -11760,10 +11760,10 @@
         <v>179984837.637</v>
       </c>
       <c r="G407">
-        <v>0.004797906940713675</v>
+        <v>0.004797744805338905</v>
       </c>
       <c r="H407">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="408" spans="1:8">
@@ -11786,10 +11786,10 @@
         <v>173632319.486</v>
       </c>
       <c r="G408">
-        <v>0.004628566059960357</v>
+        <v>0.004628409647111578</v>
       </c>
       <c r="H408">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -11812,10 +11812,10 @@
         <v>157978614.032</v>
       </c>
       <c r="G409">
-        <v>0.004211280787313621</v>
+        <v>0.004211138475760449</v>
       </c>
       <c r="H409">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -11838,10 +11838,10 @@
         <v>125346177.252</v>
       </c>
       <c r="G410">
-        <v>0.003341388650983042</v>
+        <v>0.003341275735641442</v>
       </c>
       <c r="H410">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -11864,10 +11864,10 @@
         <v>81759835.85599999</v>
       </c>
       <c r="G411">
-        <v>0.002179495167900031</v>
+        <v>0.002179421516353592</v>
       </c>
       <c r="H411">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -11890,10 +11890,10 @@
         <v>38250428.743</v>
       </c>
       <c r="G412">
-        <v>0.001019652543851763</v>
+        <v>0.001019618086795931</v>
       </c>
       <c r="H412">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -11916,10 +11916,10 @@
         <v>25395447.613</v>
       </c>
       <c r="G413">
-        <v>0.0006769736604740266</v>
+        <v>0.0006769507835446684</v>
       </c>
       <c r="H413">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -11942,10 +11942,10 @@
         <v>20375583.029</v>
       </c>
       <c r="G414">
-        <v>0.0005431577043900393</v>
+        <v>0.0005431393494950719</v>
       </c>
       <c r="H414">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -11968,10 +11968,10 @@
         <v>20190109.398</v>
       </c>
       <c r="G415">
-        <v>0.0005382134811255828</v>
+        <v>0.0005381952933104487</v>
       </c>
       <c r="H415">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -11994,10 +11994,10 @@
         <v>14166111.166</v>
       </c>
       <c r="G416">
-        <v>0.0003776300491675449</v>
+        <v>0.0003776172879384709</v>
       </c>
       <c r="H416">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -12020,10 +12020,10 @@
         <v>12331529.77</v>
       </c>
       <c r="G417">
-        <v>0.0003287250917903847</v>
+        <v>0.0003287139832035337</v>
       </c>
       <c r="H417">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -12046,10 +12046,10 @@
         <v>11807881.867</v>
       </c>
       <c r="G418">
-        <v>0.0003147660609004549</v>
+        <v>0.0003147554240302782</v>
       </c>
       <c r="H418">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -12072,10 +12072,10 @@
         <v>11198667.289</v>
       </c>
       <c r="G419">
-        <v>0.0002985260548502494</v>
+        <v>0.0002985159667776003</v>
       </c>
       <c r="H419">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="420" spans="1:8">
@@ -12098,10 +12098,10 @@
         <v>11075884.791</v>
       </c>
       <c r="G420">
-        <v>0.0002952530069252876</v>
+        <v>0.0002952430294585462</v>
       </c>
       <c r="H420">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -12124,10 +12124,10 @@
         <v>10648152.453</v>
       </c>
       <c r="G421">
-        <v>0.0002838508244959161</v>
+        <v>0.0002838412323424256</v>
       </c>
       <c r="H421">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="422" spans="1:8">
@@ -12150,10 +12150,10 @@
         <v>10164556.621</v>
       </c>
       <c r="G422">
-        <v>0.0002709594730392308</v>
+        <v>0.0002709503165223889</v>
       </c>
       <c r="H422">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="423" spans="1:8">
@@ -12176,10 +12176,10 @@
         <v>10033873.049</v>
       </c>
       <c r="G423">
-        <v>0.0002674758039403892</v>
+        <v>0.0002674667651469633</v>
       </c>
       <c r="H423">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="424" spans="1:8">
@@ -12202,10 +12202,10 @@
         <v>9723841.971000001</v>
       </c>
       <c r="G424">
-        <v>0.0002592112174313123</v>
+        <v>0.0002592024579225511</v>
       </c>
       <c r="H424">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="425" spans="1:8">
@@ -12228,10 +12228,10 @@
         <v>9382162.718</v>
       </c>
       <c r="G425">
-        <v>0.0002501029765317491</v>
+        <v>0.0002500945248172136</v>
       </c>
       <c r="H425">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="426" spans="1:8">
@@ -12254,10 +12254,10 @@
         <v>8425289.828</v>
       </c>
       <c r="G426">
-        <v>0.0002245953441078944</v>
+        <v>0.0002245877543712159</v>
       </c>
       <c r="H426">
-        <v>37513198955.507</v>
+        <v>37514466679.577</v>
       </c>
     </row>
     <row r="427" spans="1:8">
@@ -12277,13 +12277,13 @@
         <v>132</v>
       </c>
       <c r="F427">
-        <v>20455123818.176</v>
+        <v>20416325533.354</v>
       </c>
       <c r="G427">
-        <v>0.8539566793205047</v>
+        <v>0.85385865697546</v>
       </c>
       <c r="H427">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="428" spans="1:8">
@@ -12306,10 +12306,10 @@
         <v>1370737895.533</v>
       </c>
       <c r="G428">
-        <v>0.05722530901758758</v>
+        <v>0.05732747631953043</v>
       </c>
       <c r="H428">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="429" spans="1:8">
@@ -12329,13 +12329,13 @@
         <v>226</v>
       </c>
       <c r="F429">
-        <v>1027146489.234</v>
+        <v>1024672836.262</v>
       </c>
       <c r="G429">
-        <v>0.04288111931850415</v>
+        <v>0.04285422322349568</v>
       </c>
       <c r="H429">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="430" spans="1:8">
@@ -12358,10 +12358,10 @@
         <v>370373342.231</v>
       </c>
       <c r="G430">
-        <v>0.01546227694595421</v>
+        <v>0.0154898825481708</v>
       </c>
       <c r="H430">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="431" spans="1:8">
@@ -12381,13 +12381,13 @@
         <v>219</v>
       </c>
       <c r="F431">
-        <v>208809654.686</v>
+        <v>207489566.637</v>
       </c>
       <c r="G431">
-        <v>0.008717346368114933</v>
+        <v>0.008677700716304361</v>
       </c>
       <c r="H431">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="432" spans="1:8">
@@ -12407,13 +12407,13 @@
         <v>218</v>
       </c>
       <c r="F432">
-        <v>102046877.433</v>
+        <v>102046489.64</v>
       </c>
       <c r="G432">
-        <v>0.004260233932696962</v>
+        <v>0.00426782373011841</v>
       </c>
       <c r="H432">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="433" spans="1:8">
@@ -12433,13 +12433,13 @@
         <v>169</v>
       </c>
       <c r="F433">
-        <v>98491962.646</v>
+        <v>98401995.729</v>
       </c>
       <c r="G433">
-        <v>0.004111824015760826</v>
+        <v>0.004115402440052387</v>
       </c>
       <c r="H433">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="434" spans="1:8">
@@ -12462,10 +12462,10 @@
         <v>32899432.264</v>
       </c>
       <c r="G434">
-        <v>0.001373479338351937</v>
+        <v>0.001375931482004504</v>
       </c>
       <c r="H434">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="435" spans="1:8">
@@ -12485,13 +12485,13 @@
         <v>138</v>
       </c>
       <c r="F435">
-        <v>25910778.708</v>
+        <v>25910614.887</v>
       </c>
       <c r="G435">
-        <v>0.001081718338191178</v>
+        <v>0.001083642734471409</v>
       </c>
       <c r="H435">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="436" spans="1:8">
@@ -12514,10 +12514,10 @@
         <v>21009422.082</v>
       </c>
       <c r="G436">
-        <v>0.0008770974194566099</v>
+        <v>0.0008786633468133213</v>
       </c>
       <c r="H436">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="437" spans="1:8">
@@ -12537,13 +12537,13 @@
         <v>139</v>
       </c>
       <c r="F437">
-        <v>17082292.629</v>
+        <v>17053095.621</v>
       </c>
       <c r="G437">
-        <v>0.0007131483543345649</v>
+        <v>0.0007132004875428278</v>
       </c>
       <c r="H437">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="438" spans="1:8">
@@ -12563,13 +12563,13 @@
         <v>152</v>
       </c>
       <c r="F438">
-        <v>16311710.691</v>
+        <v>16311797.407</v>
       </c>
       <c r="G438">
-        <v>0.0006809782438640472</v>
+        <v>0.0006821976561866037</v>
       </c>
       <c r="H438">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="439" spans="1:8">
@@ -12592,10 +12592,10 @@
         <v>13641165.562</v>
       </c>
       <c r="G439">
-        <v>0.0005694888258283588</v>
+        <v>0.0005705055636637735</v>
       </c>
       <c r="H439">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="440" spans="1:8">
@@ -12618,10 +12618,10 @@
         <v>10549440.04</v>
       </c>
       <c r="G440">
-        <v>0.0004404160476038854</v>
+        <v>0.0004412023451370659</v>
       </c>
       <c r="H440">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="441" spans="1:8">
@@ -12644,10 +12644,10 @@
         <v>9266807.626</v>
       </c>
       <c r="G441">
-        <v>0.0003868689497332282</v>
+        <v>0.0003875596468649389</v>
       </c>
       <c r="H441">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -12670,10 +12670,10 @@
         <v>9202796.619999999</v>
       </c>
       <c r="G442">
-        <v>0.0003841966302396081</v>
+        <v>0.0003848825563412049</v>
       </c>
       <c r="H442">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="443" spans="1:8">
@@ -12696,10 +12696,10 @@
         <v>8494783</v>
       </c>
       <c r="G443">
-        <v>0.0003546386101942029</v>
+        <v>0.0003552717648348737</v>
       </c>
       <c r="H443">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="444" spans="1:8">
@@ -12722,10 +12722,10 @@
         <v>8154984.628</v>
       </c>
       <c r="G444">
-        <v>0.0003404527713808592</v>
+        <v>0.0003410605993102856</v>
       </c>
       <c r="H444">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="445" spans="1:8">
@@ -12748,10 +12748,10 @@
         <v>7688139.907</v>
       </c>
       <c r="G445">
-        <v>0.0003209630253765245</v>
+        <v>0.0003215360572550601</v>
       </c>
       <c r="H445">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="446" spans="1:8">
@@ -12774,10 +12774,10 @@
         <v>7626408.823</v>
       </c>
       <c r="G446">
-        <v>0.0003183858876396875</v>
+        <v>0.0003189543184210193</v>
       </c>
       <c r="H446">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="447" spans="1:8">
@@ -12800,10 +12800,10 @@
         <v>7206313.186</v>
       </c>
       <c r="G447">
-        <v>0.0003008478136412901</v>
+        <v>0.0003013849327926377</v>
       </c>
       <c r="H447">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="448" spans="1:8">
@@ -12826,10 +12826,10 @@
         <v>6362837.609999999</v>
       </c>
       <c r="G448">
-        <v>0.0002656345532195235</v>
+        <v>0.0002661088043170037</v>
       </c>
       <c r="H448">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="449" spans="1:8">
@@ -12852,10 +12852,10 @@
         <v>6077614.216999999</v>
       </c>
       <c r="G449">
-        <v>0.0002537271004113241</v>
+        <v>0.0002541800925178558</v>
       </c>
       <c r="H449">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="450" spans="1:8">
@@ -12878,10 +12878,10 @@
         <v>5674198.789</v>
       </c>
       <c r="G450">
-        <v>0.0002368853886552004</v>
+        <v>0.0002373083123832513</v>
       </c>
       <c r="H450">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="451" spans="1:8">
@@ -12904,10 +12904,10 @@
         <v>5037026.188999999</v>
       </c>
       <c r="G451">
-        <v>0.0002102848262490946</v>
+        <v>0.0002106602586182022</v>
       </c>
       <c r="H451">
-        <v>23953350695.087</v>
+        <v>23910661754.807</v>
       </c>
     </row>
     <row r="452" spans="1:8">
@@ -12927,13 +12927,13 @@
         <v>132</v>
       </c>
       <c r="F452">
-        <v>27281641535.979</v>
+        <v>27291272881.92</v>
       </c>
       <c r="G452">
-        <v>0.8150685462760994</v>
+        <v>0.8151180811466293</v>
       </c>
       <c r="H452">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="453" spans="1:8">
@@ -12956,10 +12956,10 @@
         <v>2380793711.316</v>
       </c>
       <c r="G453">
-        <v>0.07112878697956898</v>
+        <v>0.07110800621027437</v>
       </c>
       <c r="H453">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="454" spans="1:8">
@@ -12982,10 +12982,10 @@
         <v>2317951676.75</v>
       </c>
       <c r="G454">
-        <v>0.06925131323257351</v>
+        <v>0.06923108098027812</v>
       </c>
       <c r="H454">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="455" spans="1:8">
@@ -13005,13 +13005,13 @@
         <v>158</v>
       </c>
       <c r="F455">
-        <v>487837028.946</v>
+        <v>487987405.429</v>
       </c>
       <c r="G455">
-        <v>0.01457465884075509</v>
+        <v>0.01457489210041657</v>
       </c>
       <c r="H455">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="456" spans="1:8">
@@ -13034,10 +13034,10 @@
         <v>200532533.354</v>
       </c>
       <c r="G456">
-        <v>0.005991126312042238</v>
+        <v>0.005989375962865874</v>
       </c>
       <c r="H456">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="457" spans="1:8">
@@ -13060,10 +13060,10 @@
         <v>127828057.435</v>
       </c>
       <c r="G457">
-        <v>0.003819001463289492</v>
+        <v>0.003817885715478874</v>
       </c>
       <c r="H457">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="458" spans="1:8">
@@ -13083,13 +13083,13 @@
         <v>169</v>
       </c>
       <c r="F458">
-        <v>88804758.33</v>
+        <v>88871966.682</v>
       </c>
       <c r="G458">
-        <v>0.002653138198409951</v>
+        <v>0.002654370401226321</v>
       </c>
       <c r="H458">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="459" spans="1:8">
@@ -13112,10 +13112,10 @@
         <v>56497098.281</v>
       </c>
       <c r="G459">
-        <v>0.001687911913364275</v>
+        <v>0.00168741877817175</v>
       </c>
       <c r="H459">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -13135,13 +13135,13 @@
         <v>218</v>
       </c>
       <c r="F460">
-        <v>46946301.998</v>
+        <v>46946476.77</v>
       </c>
       <c r="G460">
-        <v>0.001402571545120754</v>
+        <v>0.001402166994076278</v>
       </c>
       <c r="H460">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="461" spans="1:8">
@@ -13164,10 +13164,10 @@
         <v>41082546.981</v>
       </c>
       <c r="G461">
-        <v>0.001227385522273765</v>
+        <v>0.001227026933065977</v>
       </c>
       <c r="H461">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -13187,13 +13187,13 @@
         <v>138</v>
       </c>
       <c r="F462">
-        <v>29225966.339</v>
+        <v>29226037.26</v>
       </c>
       <c r="G462">
-        <v>0.0008731573525745368</v>
+        <v>0.0008729043718101254</v>
       </c>
       <c r="H462">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="463" spans="1:8">
@@ -13216,10 +13216,10 @@
         <v>28458060.696</v>
       </c>
       <c r="G463">
-        <v>0.0008502153409917005</v>
+        <v>0.0008499669446728238</v>
       </c>
       <c r="H463">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="464" spans="1:8">
@@ -13242,10 +13242,10 @@
         <v>25800378.664</v>
       </c>
       <c r="G464">
-        <v>0.0007708142159740001</v>
+        <v>0.0007705890172454492</v>
       </c>
       <c r="H464">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="465" spans="1:8">
@@ -13268,10 +13268,10 @@
         <v>25079843.737</v>
       </c>
       <c r="G465">
-        <v>0.0007492874557636025</v>
+        <v>0.0007490685462276077</v>
       </c>
       <c r="H465">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="466" spans="1:8">
@@ -13291,13 +13291,13 @@
         <v>139</v>
       </c>
       <c r="F466">
-        <v>24589486.17</v>
+        <v>24616137.062</v>
       </c>
       <c r="G466">
-        <v>0.0007346374931224952</v>
+        <v>0.0007352188552741569</v>
       </c>
       <c r="H466">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -13320,10 +13320,10 @@
         <v>24492427.367</v>
       </c>
       <c r="G467">
-        <v>0.0007317377564127308</v>
+        <v>0.0007315239741433307</v>
       </c>
       <c r="H467">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -13346,10 +13346,10 @@
         <v>21086664.896</v>
       </c>
       <c r="G468">
-        <v>0.0006299869192228656</v>
+        <v>0.0006298028641674806</v>
       </c>
       <c r="H468">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -13372,10 +13372,10 @@
         <v>17049997.767</v>
       </c>
       <c r="G469">
-        <v>0.0005093871230450775</v>
+        <v>0.000509238302058032</v>
       </c>
       <c r="H469">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="470" spans="1:8">
@@ -13398,10 +13398,10 @@
         <v>13474702.478</v>
       </c>
       <c r="G470">
-        <v>0.0004025713095658962</v>
+        <v>0.0004024536955608785</v>
       </c>
       <c r="H470">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -13424,10 +13424,10 @@
         <v>13144124</v>
       </c>
       <c r="G471">
-        <v>0.000392694920011467</v>
+        <v>0.0003925801914622754</v>
       </c>
       <c r="H471">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -13450,10 +13450,10 @@
         <v>12726848.288</v>
       </c>
       <c r="G472">
-        <v>0.0003802283568272968</v>
+        <v>0.0003801172704711529</v>
       </c>
       <c r="H472">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="473" spans="1:8">
@@ -13476,10 +13476,10 @@
         <v>11715005</v>
       </c>
       <c r="G473">
-        <v>0.0003499984442788987</v>
+        <v>0.000349896189801733</v>
       </c>
       <c r="H473">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="474" spans="1:8">
@@ -13502,10 +13502,10 @@
         <v>9778894.716</v>
       </c>
       <c r="G474">
-        <v>0.0002921550556203043</v>
+        <v>0.0002920697004910113</v>
       </c>
       <c r="H474">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="475" spans="1:8">
@@ -13528,10 +13528,10 @@
         <v>9461755.129000001</v>
       </c>
       <c r="G475">
-        <v>0.0002826801674688053</v>
+        <v>0.0002825975804939139</v>
       </c>
       <c r="H475">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="476" spans="1:8">
@@ -13551,13 +13551,13 @@
         <v>147</v>
       </c>
       <c r="F476">
-        <v>8633134.026000001</v>
+        <v>8493939.58</v>
       </c>
       <c r="G476">
-        <v>0.0002579242158540458</v>
+        <v>0.0002536914918472619</v>
       </c>
       <c r="H476">
-        <v>33471591635.604</v>
+        <v>33481373451.475</v>
       </c>
     </row>
     <row r="477" spans="1:8">
@@ -13577,13 +13577,13 @@
         <v>132</v>
       </c>
       <c r="F477">
-        <v>41065463127.394</v>
+        <v>41059734422.731</v>
       </c>
       <c r="G477">
-        <v>0.7720430423440157</v>
+        <v>0.772089594052851</v>
       </c>
       <c r="H477">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="478" spans="1:8">
@@ -13603,13 +13603,13 @@
         <v>226</v>
       </c>
       <c r="F478">
-        <v>6846389242.389</v>
+        <v>6837573412.245</v>
       </c>
       <c r="G478">
-        <v>0.1287141743261955</v>
+        <v>0.1285741214449792</v>
       </c>
       <c r="H478">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="479" spans="1:8">
@@ -13629,13 +13629,13 @@
         <v>133</v>
       </c>
       <c r="F479">
-        <v>2904418046.17</v>
+        <v>2908381801.008</v>
       </c>
       <c r="G479">
-        <v>0.05460393171867405</v>
+        <v>0.05468937769962347</v>
       </c>
       <c r="H479">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="480" spans="1:8">
@@ -13655,13 +13655,13 @@
         <v>219</v>
       </c>
       <c r="F480">
-        <v>484592442.252</v>
+        <v>484710997.031</v>
       </c>
       <c r="G480">
-        <v>0.009110483479816843</v>
+        <v>0.009114533305978596</v>
       </c>
       <c r="H480">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="481" spans="1:8">
@@ -13684,10 +13684,10 @@
         <v>479676252.479</v>
       </c>
       <c r="G481">
-        <v>0.009018057635322823</v>
+        <v>0.009019859681514978</v>
       </c>
       <c r="H481">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="482" spans="1:8">
@@ -13710,10 +13710,10 @@
         <v>298425321.84</v>
       </c>
       <c r="G482">
-        <v>0.00561048569380804</v>
+        <v>0.005611606817090848</v>
       </c>
       <c r="H482">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="483" spans="1:8">
@@ -13733,13 +13733,13 @@
         <v>157</v>
       </c>
       <c r="F483">
-        <v>136613033.914</v>
+        <v>136679032.338</v>
       </c>
       <c r="G483">
-        <v>0.002568366074421621</v>
+        <v>0.002570120339964048</v>
       </c>
       <c r="H483">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="484" spans="1:8">
@@ -13762,10 +13762,10 @@
         <v>121088095.198</v>
       </c>
       <c r="G484">
-        <v>0.00227649256306435</v>
+        <v>0.002276947466428315</v>
       </c>
       <c r="H484">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="485" spans="1:8">
@@ -13788,10 +13788,10 @@
         <v>83596296.13600001</v>
       </c>
       <c r="G485">
-        <v>0.001571635478633512</v>
+        <v>0.001571949532928157</v>
       </c>
       <c r="H485">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="486" spans="1:8">
@@ -13811,13 +13811,13 @@
         <v>218</v>
       </c>
       <c r="F486">
-        <v>80958023.50400001</v>
+        <v>80730717.13</v>
       </c>
       <c r="G486">
-        <v>0.001522035160647972</v>
+        <v>0.001518065021433507</v>
       </c>
       <c r="H486">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="487" spans="1:8">
@@ -13837,13 +13837,13 @@
         <v>138</v>
       </c>
       <c r="F487">
-        <v>60255226.677</v>
+        <v>60255337.056</v>
       </c>
       <c r="G487">
-        <v>0.0011328163614404</v>
+        <v>0.001133044803653906</v>
       </c>
       <c r="H487">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="488" spans="1:8">
@@ -13866,10 +13866,10 @@
         <v>49062341.047</v>
       </c>
       <c r="G488">
-        <v>0.0009223867493942299</v>
+        <v>0.0009225710666382149</v>
       </c>
       <c r="H488">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="489" spans="1:8">
@@ -13892,10 +13892,10 @@
         <v>43387322.355</v>
       </c>
       <c r="G489">
-        <v>0.000815694693280339</v>
+        <v>0.0008158576906324771</v>
       </c>
       <c r="H489">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="490" spans="1:8">
@@ -13918,10 +13918,10 @@
         <v>39729031.141</v>
       </c>
       <c r="G490">
-        <v>0.0007469177195524362</v>
+        <v>0.0007470669734479869</v>
       </c>
       <c r="H490">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="491" spans="1:8">
@@ -13944,10 +13944,10 @@
         <v>39404625.118</v>
       </c>
       <c r="G491">
-        <v>0.0007408187888725441</v>
+        <v>0.0007409668240405979</v>
       </c>
       <c r="H491">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="492" spans="1:8">
@@ -13970,10 +13970,10 @@
         <v>35467949.924</v>
       </c>
       <c r="G492">
-        <v>0.0006668081126975923</v>
+        <v>0.0006669413585770241</v>
       </c>
       <c r="H492">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="493" spans="1:8">
@@ -13996,10 +13996,10 @@
         <v>35032721.869</v>
       </c>
       <c r="G493">
-        <v>0.0006586256945265546</v>
+        <v>0.0006587573053426386</v>
       </c>
       <c r="H493">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="494" spans="1:8">
@@ -14022,10 +14022,10 @@
         <v>25265431.805</v>
       </c>
       <c r="G494">
-        <v>0.0004749977073521756</v>
+        <v>0.000475092624444573</v>
       </c>
       <c r="H494">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="495" spans="1:8">
@@ -14045,13 +14045,13 @@
         <v>222</v>
       </c>
       <c r="F495">
-        <v>24684439.446</v>
+        <v>24683383.119</v>
       </c>
       <c r="G495">
-        <v>0.000464074876480173</v>
+        <v>0.0004641477476690441</v>
       </c>
       <c r="H495">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="496" spans="1:8">
@@ -14074,10 +14074,10 @@
         <v>24352513.958</v>
       </c>
       <c r="G496">
-        <v>0.0004578345775995281</v>
+        <v>0.0004579260650451138</v>
       </c>
       <c r="H496">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="497" spans="1:8">
@@ -14100,10 +14100,10 @@
         <v>21997427.519</v>
       </c>
       <c r="G497">
-        <v>0.0004135582451079608</v>
+        <v>0.000413640884972438</v>
       </c>
       <c r="H497">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="498" spans="1:8">
@@ -14126,10 +14126,10 @@
         <v>20528476.088</v>
       </c>
       <c r="G498">
-        <v>0.0003859415169506128</v>
+        <v>0.0003860186382631105</v>
       </c>
       <c r="H498">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="499" spans="1:8">
@@ -14149,13 +14149,13 @@
         <v>139</v>
       </c>
       <c r="F499">
-        <v>18231023.785</v>
+        <v>18229841.554</v>
       </c>
       <c r="G499">
-        <v>0.0003427487235284156</v>
+        <v>0.0003427949830402114</v>
       </c>
       <c r="H499">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="500" spans="1:8">
@@ -14178,10 +14178,10 @@
         <v>11851514.579</v>
       </c>
       <c r="G500">
-        <v>0.0002228120341312285</v>
+        <v>0.0002228565578628245</v>
       </c>
       <c r="H500">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="501" spans="1:8">
@@ -14204,10 +14204,10 @@
         <v>11758787.779</v>
       </c>
       <c r="G501">
-        <v>0.0002210687424372631</v>
+        <v>0.0002211129178131172</v>
       </c>
       <c r="H501">
-        <v>53190639478.745</v>
+        <v>53180012707.075</v>
       </c>
     </row>
     <row r="502" spans="1:8">
@@ -14227,13 +14227,13 @@
         <v>132</v>
       </c>
       <c r="F502">
-        <v>32592735534.759</v>
+        <v>32600047625.784</v>
       </c>
       <c r="G502">
-        <v>0.8117844625862143</v>
+        <v>0.8118020383045212</v>
       </c>
       <c r="H502">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="503" spans="1:8">
@@ -14253,13 +14253,13 @@
         <v>133</v>
       </c>
       <c r="F503">
-        <v>3272362612.352</v>
+        <v>3277210592.838</v>
       </c>
       <c r="G503">
-        <v>0.08150445432303083</v>
+        <v>0.08160866112093834</v>
       </c>
       <c r="H503">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="504" spans="1:8">
@@ -14279,13 +14279,13 @@
         <v>226</v>
       </c>
       <c r="F504">
-        <v>2734532631.748</v>
+        <v>2734817901.551</v>
       </c>
       <c r="G504">
-        <v>0.06810876922314862</v>
+        <v>0.06810207065816834</v>
       </c>
       <c r="H504">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="505" spans="1:8">
@@ -14308,10 +14308,10 @@
         <v>414996529.849</v>
       </c>
       <c r="G505">
-        <v>0.01033628289958465</v>
+        <v>0.01033418824070259</v>
       </c>
       <c r="H505">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="506" spans="1:8">
@@ -14334,10 +14334,10 @@
         <v>149952566.526</v>
       </c>
       <c r="G506">
-        <v>0.003734855685890882</v>
+        <v>0.003734098813356368</v>
       </c>
       <c r="H506">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="507" spans="1:8">
@@ -14357,13 +14357,13 @@
         <v>157</v>
       </c>
       <c r="F507">
-        <v>147752902.857</v>
+        <v>147824124.819</v>
       </c>
       <c r="G507">
-        <v>0.003680068851950379</v>
+        <v>0.003681096641826154</v>
       </c>
       <c r="H507">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="508" spans="1:8">
@@ -14383,13 +14383,13 @@
         <v>218</v>
       </c>
       <c r="F508">
-        <v>105302238.448</v>
+        <v>105302241.927</v>
       </c>
       <c r="G508">
-        <v>0.002622753802192233</v>
+        <v>0.00262222238493796</v>
       </c>
       <c r="H508">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="509" spans="1:8">
@@ -14412,10 +14412,10 @@
         <v>81762390.34999999</v>
       </c>
       <c r="G509">
-        <v>0.002036448828888698</v>
+        <v>0.002036036140336272</v>
       </c>
       <c r="H509">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="510" spans="1:8">
@@ -14438,10 +14438,10 @@
         <v>43097495.739</v>
       </c>
       <c r="G510">
-        <v>0.00107342562209866</v>
+        <v>0.001073208091238156</v>
       </c>
       <c r="H510">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="511" spans="1:8">
@@ -14464,10 +14464,10 @@
         <v>42918112.292</v>
       </c>
       <c r="G511">
-        <v>0.001068957734002417</v>
+        <v>0.001068741108564256</v>
       </c>
       <c r="H511">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="512" spans="1:8">
@@ -14490,10 +14490,10 @@
         <v>42826872.733</v>
       </c>
       <c r="G512">
-        <v>0.001066685238148534</v>
+        <v>0.00106646907323411</v>
       </c>
       <c r="H512">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="513" spans="1:8">
@@ -14516,10 +14516,10 @@
         <v>40670163.548</v>
       </c>
       <c r="G513">
-        <v>0.001012968267849038</v>
+        <v>0.001012762988736604</v>
       </c>
       <c r="H513">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="514" spans="1:8">
@@ -14542,10 +14542,10 @@
         <v>31598677.612</v>
       </c>
       <c r="G514">
-        <v>0.0007870255473443228</v>
+        <v>0.0007868660557679826</v>
       </c>
       <c r="H514">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="515" spans="1:8">
@@ -14568,10 +14568,10 @@
         <v>29988107.877</v>
       </c>
       <c r="G515">
-        <v>0.0007469112253847479</v>
+        <v>0.0007467598630190348</v>
       </c>
       <c r="H515">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="516" spans="1:8">
@@ -14594,10 +14594,10 @@
         <v>27571993.971</v>
       </c>
       <c r="G516">
-        <v>0.0006867332839953987</v>
+        <v>0.0006865941167544377</v>
       </c>
       <c r="H516">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="517" spans="1:8">
@@ -14620,10 +14620,10 @@
         <v>23503181.189</v>
       </c>
       <c r="G517">
-        <v>0.0005853917137526292</v>
+        <v>0.0005852730834902217</v>
       </c>
       <c r="H517">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="518" spans="1:8">
@@ -14646,10 +14646,10 @@
         <v>23255847.182</v>
       </c>
       <c r="G518">
-        <v>0.000579231386898884</v>
+        <v>0.0005791140050333602</v>
       </c>
       <c r="H518">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="519" spans="1:8">
@@ -14672,10 +14672,10 @@
         <v>20974008.156</v>
       </c>
       <c r="G519">
-        <v>0.0005223978184046353</v>
+        <v>0.000522291953923088</v>
       </c>
       <c r="H519">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="520" spans="1:8">
@@ -14698,10 +14698,10 @@
         <v>20097674.65</v>
       </c>
       <c r="G520">
-        <v>0.0005005710550924294</v>
+        <v>0.0005004696138280177</v>
       </c>
       <c r="H520">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="521" spans="1:8">
@@ -14724,10 +14724,10 @@
         <v>19860308.423</v>
       </c>
       <c r="G521">
-        <v>0.0004946589948784038</v>
+        <v>0.0004945587516993733</v>
       </c>
       <c r="H521">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="522" spans="1:8">
@@ -14747,13 +14747,13 @@
         <v>139</v>
       </c>
       <c r="F522">
-        <v>19225357.362</v>
+        <v>19227440.967</v>
       </c>
       <c r="G522">
-        <v>0.0004788443233767518</v>
+        <v>0.0004787991707117967</v>
       </c>
       <c r="H522">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="523" spans="1:8">
@@ -14776,10 +14776,10 @@
         <v>13751139.404</v>
       </c>
       <c r="G523">
-        <v>0.0003424984472113227</v>
+        <v>0.0003424290395314524</v>
       </c>
       <c r="H523">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="524" spans="1:8">
@@ -14802,10 +14802,10 @@
         <v>11461271.848</v>
       </c>
       <c r="G524">
-        <v>0.0002854649128104241</v>
+        <v>0.0002854070630378372</v>
       </c>
       <c r="H524">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="525" spans="1:8">
@@ -14828,10 +14828,10 @@
         <v>9929562.046</v>
       </c>
       <c r="G525">
-        <v>0.0002473147484239906</v>
+        <v>0.0002472646298233792</v>
       </c>
       <c r="H525">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="526" spans="1:8">
@@ -14854,10 +14854,10 @@
         <v>9627040.652000001</v>
       </c>
       <c r="G526">
-        <v>0.0002397798740656472</v>
+        <v>0.0002397312824154544</v>
       </c>
       <c r="H526">
-        <v>40149494153.81</v>
+        <v>40157632141.292</v>
       </c>
     </row>
     <row r="527" spans="1:8">
@@ -14877,13 +14877,13 @@
         <v>132</v>
       </c>
       <c r="F527">
-        <v>33038692346.637</v>
+        <v>33055511956.291</v>
       </c>
       <c r="G527">
-        <v>0.8690251146685165</v>
+        <v>0.8690753647162807</v>
       </c>
       <c r="H527">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="528" spans="1:8">
@@ -14903,13 +14903,13 @@
         <v>133</v>
       </c>
       <c r="F528">
-        <v>2012895937.947</v>
+        <v>1995425809.648</v>
       </c>
       <c r="G528">
-        <v>0.05294571301240496</v>
+        <v>0.0524625186739567</v>
       </c>
       <c r="H528">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="529" spans="1:8">
@@ -14929,13 +14929,13 @@
         <v>226</v>
       </c>
       <c r="F529">
-        <v>1828601047.939</v>
+        <v>1831869793.124</v>
       </c>
       <c r="G529">
-        <v>0.04809815772051623</v>
+        <v>0.04816240361598721</v>
       </c>
       <c r="H529">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="530" spans="1:8">
@@ -14955,13 +14955,13 @@
         <v>158</v>
       </c>
       <c r="F530">
-        <v>385740159.104</v>
+        <v>385835265.227</v>
       </c>
       <c r="G530">
-        <v>0.01014622136011164</v>
+        <v>0.01014414552982717</v>
       </c>
       <c r="H530">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="531" spans="1:8">
@@ -14981,13 +14981,13 @@
         <v>219</v>
       </c>
       <c r="F531">
-        <v>140545341.746</v>
+        <v>140303644.163</v>
       </c>
       <c r="G531">
-        <v>0.003696799814154141</v>
+        <v>0.003688777862016334</v>
       </c>
       <c r="H531">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="532" spans="1:8">
@@ -15007,13 +15007,13 @@
         <v>157</v>
       </c>
       <c r="F532">
-        <v>106720437.084</v>
+        <v>106540464.606</v>
       </c>
       <c r="G532">
-        <v>0.002807094757303177</v>
+        <v>0.002801096932243391</v>
       </c>
       <c r="H532">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="533" spans="1:8">
@@ -15033,13 +15033,13 @@
         <v>218</v>
       </c>
       <c r="F533">
-        <v>84438057.09199999</v>
+        <v>84437809.763</v>
       </c>
       <c r="G533">
-        <v>0.002220995657966204</v>
+        <v>0.002219987408231843</v>
       </c>
       <c r="H533">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="534" spans="1:8">
@@ -15062,10 +15062,10 @@
         <v>49105048.374</v>
       </c>
       <c r="G534">
-        <v>0.001291622557160987</v>
+        <v>0.001291039989986382</v>
       </c>
       <c r="H534">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="535" spans="1:8">
@@ -15088,10 +15088,10 @@
         <v>38051421.564</v>
       </c>
       <c r="G535">
-        <v>0.001000876204209732</v>
+        <v>0.001000424773860221</v>
       </c>
       <c r="H535">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="536" spans="1:8">
@@ -15114,10 +15114,10 @@
         <v>27066847.374</v>
       </c>
       <c r="G536">
-        <v>0.000711946159857621</v>
+        <v>0.000711625047114181</v>
       </c>
       <c r="H536">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="537" spans="1:8">
@@ -15140,10 +15140,10 @@
         <v>22215568.177</v>
       </c>
       <c r="G537">
-        <v>0.0005843417312007753</v>
+        <v>0.0005840781725400335</v>
       </c>
       <c r="H537">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="538" spans="1:8">
@@ -15163,13 +15163,13 @@
         <v>138</v>
       </c>
       <c r="F538">
-        <v>20774117.937</v>
+        <v>20870427.576</v>
       </c>
       <c r="G538">
-        <v>0.0005464268994948992</v>
+        <v>0.0005487125560596551</v>
       </c>
       <c r="H538">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="539" spans="1:8">
@@ -15189,13 +15189,13 @@
         <v>264</v>
       </c>
       <c r="F539">
-        <v>20433560.51</v>
+        <v>20420657.437</v>
       </c>
       <c r="G539">
-        <v>0.0005374691310110623</v>
+        <v>0.0005368874738129549</v>
       </c>
       <c r="H539">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="540" spans="1:8">
@@ -15218,10 +15218,10 @@
         <v>19669941.972</v>
       </c>
       <c r="G540">
-        <v>0.0005173834786920775</v>
+        <v>0.0005171501205568405</v>
       </c>
       <c r="H540">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="541" spans="1:8">
@@ -15241,13 +15241,13 @@
         <v>222</v>
       </c>
       <c r="F541">
-        <v>19448389.445</v>
+        <v>19449072.483</v>
       </c>
       <c r="G541">
-        <v>0.0005115559263131507</v>
+        <v>0.0005113431546274915</v>
       </c>
       <c r="H541">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="542" spans="1:8">
@@ -15261,19 +15261,19 @@
         <v>16</v>
       </c>
       <c r="D542" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E542" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="F542">
-        <v>13466447.263</v>
+        <v>14381567.853</v>
       </c>
       <c r="G542">
-        <v>0.0003542113820402858</v>
+        <v>0.0003781114128126281</v>
       </c>
       <c r="H542">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="543" spans="1:8">
@@ -15287,19 +15287,19 @@
         <v>17</v>
       </c>
       <c r="D543" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E543" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F543">
-        <v>12277661</v>
+        <v>13466447.263</v>
       </c>
       <c r="G543">
-        <v>0.0003229424350831557</v>
+        <v>0.0003540516202562383</v>
       </c>
       <c r="H543">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="544" spans="1:8">
@@ -15313,19 +15313,19 @@
         <v>18</v>
       </c>
       <c r="D544" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E544" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F544">
-        <v>10976419.316</v>
+        <v>12277661</v>
       </c>
       <c r="G544">
-        <v>0.000288715544630433</v>
+        <v>0.0003227967766933085</v>
       </c>
       <c r="H544">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="545" spans="1:8">
@@ -15339,19 +15339,19 @@
         <v>19</v>
       </c>
       <c r="D545" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E545" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F545">
-        <v>10440132.436</v>
+        <v>10458007.957</v>
       </c>
       <c r="G545">
-        <v>0.0002746094546406256</v>
+        <v>0.0002749555684224033</v>
       </c>
       <c r="H545">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="546" spans="1:8">
@@ -15365,19 +15365,19 @@
         <v>20</v>
       </c>
       <c r="D546" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E546" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F546">
-        <v>9013719.023</v>
+        <v>9073697.372000001</v>
       </c>
       <c r="G546">
-        <v>0.0002370901404137957</v>
+        <v>0.0002385601186066421</v>
       </c>
       <c r="H546">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="547" spans="1:8">
@@ -15391,19 +15391,19 @@
         <v>21</v>
       </c>
       <c r="D547" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E547" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F547">
-        <v>8133886.099</v>
+        <v>8940141.363</v>
       </c>
       <c r="G547">
-        <v>0.0002139476715882683</v>
+        <v>0.0002350487454539526</v>
       </c>
       <c r="H547">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="548" spans="1:8">
@@ -15417,19 +15417,19 @@
         <v>22</v>
       </c>
       <c r="D548" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="E548" t="s">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="F548">
-        <v>7081464.361</v>
+        <v>8133886.099</v>
       </c>
       <c r="G548">
-        <v>0.000186265555360742</v>
+        <v>0.0002138511736679901</v>
       </c>
       <c r="H548">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="549" spans="1:8">
@@ -15443,19 +15443,19 @@
         <v>23</v>
       </c>
       <c r="D549" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E549" t="s">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="F549">
-        <v>4820162.902</v>
+        <v>7075571.51</v>
       </c>
       <c r="G549">
-        <v>0.000126785968847761</v>
+        <v>0.0001860266118026068</v>
       </c>
       <c r="H549">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="550" spans="1:8">
@@ -15469,19 +15469,19 @@
         <v>24</v>
       </c>
       <c r="D550" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="E550" t="s">
-        <v>153</v>
+        <v>252</v>
       </c>
       <c r="F550">
-        <v>4747988.335</v>
+        <v>4835798.534</v>
       </c>
       <c r="G550">
-        <v>0.0001248875428838863</v>
+        <v>0.0001271398664219045</v>
       </c>
       <c r="H550">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
     <row r="551" spans="1:8">
@@ -15495,19 +15495,19 @@
         <v>25</v>
       </c>
       <c r="D551" t="s">
-        <v>124</v>
+        <v>30</v>
       </c>
       <c r="E551" t="s">
-        <v>262</v>
+        <v>153</v>
       </c>
       <c r="F551">
-        <v>4537449.99</v>
+        <v>4764681.869</v>
       </c>
       <c r="G551">
-        <v>0.0001193496993310567</v>
+        <v>0.0001252701104291973</v>
       </c>
       <c r="H551">
-        <v>38018109936.028</v>
+        <v>38035265177.586</v>
       </c>
     </row>
   </sheetData>
